--- a/docs/candidate-roster-template.xlsx
+++ b/docs/candidate-roster-template.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,18 +35,6 @@
     <font>
       <name val="Arial"/>
       <i val="1"/>
-      <color rgb="00404040"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -71,7 +59,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -85,22 +73,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00375623"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -130,52 +123,55 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -252,6 +248,24 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Resource Planning</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Row 2 is an example. Delete it before sending this back, and put one person per row from row 2 down.
+Header colours: dark blue means a CV already answers this column better. Green means nothing but this sheet holds it.
+Do not type anything below or beside the table: saving as CSV picks up every cell on this sheet, and a stray note becomes a person.
+Read the 'How to fill this in' tab first, especially the part about people who already have a TiPP Focus CV.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -638,1726 +652,1628 @@
           <t>languages</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>availability</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>available_from</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>resource_categories</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>on the CV</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>on the CV</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>on the CV</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>on the CV</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>on the CV</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>on the CV</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>on the CV</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>on the CV</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>on the CV</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>on the CV</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>on the CV</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>on the CV</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>on the CV</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>on the CV</t>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Thandiwe Mokoena</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>t.mokoena@example.co.za</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>082 555 0143</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Johannesburg</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>ERP Consultant</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Business Analyst | Systems Analyst</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>African Female</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>BCom Information Systems | Matric</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft Certified: Dynamics 365 F&amp;O Apps Developer Associate</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft Dynamics 365 | SQL | X++</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>Business Process Analysis | UAT</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>Public Sector | Finance</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>English | Setswana</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>only here</t>
-        </is>
-      </c>
-      <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>only here</t>
-        </is>
-      </c>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="P2" s="4" t="inlineStr"/>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>only here</t>
+          <t>active</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>only here</t>
+          <t>ERP | Business Analysis</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>only here</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="34" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Thandiwe Mokoena</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>t.mokoena@example.co.za</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>082 555 0143</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Johannesburg</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>ERP Consultant</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Business Analyst | Systems Analyst</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>African Female</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>BCom Information Systems | Matric</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>Microsoft Certified: Dynamics 365 F&amp;O Apps Developer Associate</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>Microsoft Dynamics 365 | SQL | X++</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>Business Process Analysis | UAT</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>Public Sector | Finance</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>English | Setswana</t>
-        </is>
-      </c>
-      <c r="O3" s="4" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="P3" s="5" t="inlineStr"/>
-      <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="R3" s="4" t="inlineStr">
-        <is>
-          <t>ERP | Business Analysis</t>
-        </is>
-      </c>
-      <c r="S3" s="4" t="inlineStr">
-        <is>
           <t>Strong on D365 Finance. Prefers Gauteng-based work.</t>
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="P3" s="5" t="n"/>
+    </row>
     <row r="4">
-      <c r="P4" s="6" t="n"/>
+      <c r="P4" s="5" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Row 2 labels where each answer comes from. Row 3 is an example: delete it, then one person per row from row 3 down. Read the 'How to fill this in' tab first, especially the part about people who already have a TiPP Focus CV.</t>
-        </is>
-      </c>
-      <c r="P5" s="6" t="n"/>
+      <c r="P5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="P6" s="6" t="n"/>
+      <c r="P6" s="5" t="n"/>
     </row>
     <row r="7">
-      <c r="P7" s="6" t="n"/>
+      <c r="P7" s="5" t="n"/>
     </row>
     <row r="8">
-      <c r="P8" s="6" t="n"/>
+      <c r="P8" s="5" t="n"/>
     </row>
     <row r="9">
-      <c r="P9" s="6" t="n"/>
+      <c r="P9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="P10" s="6" t="n"/>
+      <c r="P10" s="5" t="n"/>
     </row>
     <row r="11">
-      <c r="P11" s="6" t="n"/>
+      <c r="P11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="P12" s="6" t="n"/>
+      <c r="P12" s="5" t="n"/>
     </row>
     <row r="13">
-      <c r="P13" s="6" t="n"/>
+      <c r="P13" s="5" t="n"/>
     </row>
     <row r="14">
-      <c r="P14" s="6" t="n"/>
+      <c r="P14" s="5" t="n"/>
     </row>
     <row r="15">
-      <c r="P15" s="6" t="n"/>
+      <c r="P15" s="5" t="n"/>
     </row>
     <row r="16">
-      <c r="P16" s="6" t="n"/>
+      <c r="P16" s="5" t="n"/>
     </row>
     <row r="17">
-      <c r="P17" s="6" t="n"/>
+      <c r="P17" s="5" t="n"/>
     </row>
     <row r="18">
-      <c r="P18" s="6" t="n"/>
+      <c r="P18" s="5" t="n"/>
     </row>
     <row r="19">
-      <c r="P19" s="6" t="n"/>
+      <c r="P19" s="5" t="n"/>
     </row>
     <row r="20">
-      <c r="P20" s="6" t="n"/>
+      <c r="P20" s="5" t="n"/>
     </row>
     <row r="21">
-      <c r="P21" s="6" t="n"/>
+      <c r="P21" s="5" t="n"/>
     </row>
     <row r="22">
-      <c r="P22" s="6" t="n"/>
+      <c r="P22" s="5" t="n"/>
     </row>
     <row r="23">
-      <c r="P23" s="6" t="n"/>
+      <c r="P23" s="5" t="n"/>
     </row>
     <row r="24">
-      <c r="P24" s="6" t="n"/>
+      <c r="P24" s="5" t="n"/>
     </row>
     <row r="25">
-      <c r="P25" s="6" t="n"/>
+      <c r="P25" s="5" t="n"/>
     </row>
     <row r="26">
-      <c r="P26" s="6" t="n"/>
+      <c r="P26" s="5" t="n"/>
     </row>
     <row r="27">
-      <c r="P27" s="6" t="n"/>
+      <c r="P27" s="5" t="n"/>
     </row>
     <row r="28">
-      <c r="P28" s="6" t="n"/>
+      <c r="P28" s="5" t="n"/>
     </row>
     <row r="29">
-      <c r="P29" s="6" t="n"/>
+      <c r="P29" s="5" t="n"/>
     </row>
     <row r="30">
-      <c r="P30" s="6" t="n"/>
+      <c r="P30" s="5" t="n"/>
     </row>
     <row r="31">
-      <c r="P31" s="6" t="n"/>
+      <c r="P31" s="5" t="n"/>
     </row>
     <row r="32">
-      <c r="P32" s="6" t="n"/>
+      <c r="P32" s="5" t="n"/>
     </row>
     <row r="33">
-      <c r="P33" s="6" t="n"/>
+      <c r="P33" s="5" t="n"/>
     </row>
     <row r="34">
-      <c r="P34" s="6" t="n"/>
+      <c r="P34" s="5" t="n"/>
     </row>
     <row r="35">
-      <c r="P35" s="6" t="n"/>
+      <c r="P35" s="5" t="n"/>
     </row>
     <row r="36">
-      <c r="P36" s="6" t="n"/>
+      <c r="P36" s="5" t="n"/>
     </row>
     <row r="37">
-      <c r="P37" s="6" t="n"/>
+      <c r="P37" s="5" t="n"/>
     </row>
     <row r="38">
-      <c r="P38" s="6" t="n"/>
+      <c r="P38" s="5" t="n"/>
     </row>
     <row r="39">
-      <c r="P39" s="6" t="n"/>
+      <c r="P39" s="5" t="n"/>
     </row>
     <row r="40">
-      <c r="P40" s="6" t="n"/>
+      <c r="P40" s="5" t="n"/>
     </row>
     <row r="41">
-      <c r="P41" s="6" t="n"/>
+      <c r="P41" s="5" t="n"/>
     </row>
     <row r="42">
-      <c r="P42" s="6" t="n"/>
+      <c r="P42" s="5" t="n"/>
     </row>
     <row r="43">
-      <c r="P43" s="6" t="n"/>
+      <c r="P43" s="5" t="n"/>
     </row>
     <row r="44">
-      <c r="P44" s="6" t="n"/>
+      <c r="P44" s="5" t="n"/>
     </row>
     <row r="45">
-      <c r="P45" s="6" t="n"/>
+      <c r="P45" s="5" t="n"/>
     </row>
     <row r="46">
-      <c r="P46" s="6" t="n"/>
+      <c r="P46" s="5" t="n"/>
     </row>
     <row r="47">
-      <c r="P47" s="6" t="n"/>
+      <c r="P47" s="5" t="n"/>
     </row>
     <row r="48">
-      <c r="P48" s="6" t="n"/>
+      <c r="P48" s="5" t="n"/>
     </row>
     <row r="49">
-      <c r="P49" s="6" t="n"/>
+      <c r="P49" s="5" t="n"/>
     </row>
     <row r="50">
-      <c r="P50" s="6" t="n"/>
+      <c r="P50" s="5" t="n"/>
     </row>
     <row r="51">
-      <c r="P51" s="6" t="n"/>
+      <c r="P51" s="5" t="n"/>
     </row>
     <row r="52">
-      <c r="P52" s="6" t="n"/>
+      <c r="P52" s="5" t="n"/>
     </row>
     <row r="53">
-      <c r="P53" s="6" t="n"/>
+      <c r="P53" s="5" t="n"/>
     </row>
     <row r="54">
-      <c r="P54" s="6" t="n"/>
+      <c r="P54" s="5" t="n"/>
     </row>
     <row r="55">
-      <c r="P55" s="6" t="n"/>
+      <c r="P55" s="5" t="n"/>
     </row>
     <row r="56">
-      <c r="P56" s="6" t="n"/>
+      <c r="P56" s="5" t="n"/>
     </row>
     <row r="57">
-      <c r="P57" s="6" t="n"/>
+      <c r="P57" s="5" t="n"/>
     </row>
     <row r="58">
-      <c r="P58" s="6" t="n"/>
+      <c r="P58" s="5" t="n"/>
     </row>
     <row r="59">
-      <c r="P59" s="6" t="n"/>
+      <c r="P59" s="5" t="n"/>
     </row>
     <row r="60">
-      <c r="P60" s="6" t="n"/>
+      <c r="P60" s="5" t="n"/>
     </row>
     <row r="61">
-      <c r="P61" s="6" t="n"/>
+      <c r="P61" s="5" t="n"/>
     </row>
     <row r="62">
-      <c r="P62" s="6" t="n"/>
+      <c r="P62" s="5" t="n"/>
     </row>
     <row r="63">
-      <c r="P63" s="6" t="n"/>
+      <c r="P63" s="5" t="n"/>
     </row>
     <row r="64">
-      <c r="P64" s="6" t="n"/>
+      <c r="P64" s="5" t="n"/>
     </row>
     <row r="65">
-      <c r="P65" s="6" t="n"/>
+      <c r="P65" s="5" t="n"/>
     </row>
     <row r="66">
-      <c r="P66" s="6" t="n"/>
+      <c r="P66" s="5" t="n"/>
     </row>
     <row r="67">
-      <c r="P67" s="6" t="n"/>
+      <c r="P67" s="5" t="n"/>
     </row>
     <row r="68">
-      <c r="P68" s="6" t="n"/>
+      <c r="P68" s="5" t="n"/>
     </row>
     <row r="69">
-      <c r="P69" s="6" t="n"/>
+      <c r="P69" s="5" t="n"/>
     </row>
     <row r="70">
-      <c r="P70" s="6" t="n"/>
+      <c r="P70" s="5" t="n"/>
     </row>
     <row r="71">
-      <c r="P71" s="6" t="n"/>
+      <c r="P71" s="5" t="n"/>
     </row>
     <row r="72">
-      <c r="P72" s="6" t="n"/>
+      <c r="P72" s="5" t="n"/>
     </row>
     <row r="73">
-      <c r="P73" s="6" t="n"/>
+      <c r="P73" s="5" t="n"/>
     </row>
     <row r="74">
-      <c r="P74" s="6" t="n"/>
+      <c r="P74" s="5" t="n"/>
     </row>
     <row r="75">
-      <c r="P75" s="6" t="n"/>
+      <c r="P75" s="5" t="n"/>
     </row>
     <row r="76">
-      <c r="P76" s="6" t="n"/>
+      <c r="P76" s="5" t="n"/>
     </row>
     <row r="77">
-      <c r="P77" s="6" t="n"/>
+      <c r="P77" s="5" t="n"/>
     </row>
     <row r="78">
-      <c r="P78" s="6" t="n"/>
+      <c r="P78" s="5" t="n"/>
     </row>
     <row r="79">
-      <c r="P79" s="6" t="n"/>
+      <c r="P79" s="5" t="n"/>
     </row>
     <row r="80">
-      <c r="P80" s="6" t="n"/>
+      <c r="P80" s="5" t="n"/>
     </row>
     <row r="81">
-      <c r="P81" s="6" t="n"/>
+      <c r="P81" s="5" t="n"/>
     </row>
     <row r="82">
-      <c r="P82" s="6" t="n"/>
+      <c r="P82" s="5" t="n"/>
     </row>
     <row r="83">
-      <c r="P83" s="6" t="n"/>
+      <c r="P83" s="5" t="n"/>
     </row>
     <row r="84">
-      <c r="P84" s="6" t="n"/>
+      <c r="P84" s="5" t="n"/>
     </row>
     <row r="85">
-      <c r="P85" s="6" t="n"/>
+      <c r="P85" s="5" t="n"/>
     </row>
     <row r="86">
-      <c r="P86" s="6" t="n"/>
+      <c r="P86" s="5" t="n"/>
     </row>
     <row r="87">
-      <c r="P87" s="6" t="n"/>
+      <c r="P87" s="5" t="n"/>
     </row>
     <row r="88">
-      <c r="P88" s="6" t="n"/>
+      <c r="P88" s="5" t="n"/>
     </row>
     <row r="89">
-      <c r="P89" s="6" t="n"/>
+      <c r="P89" s="5" t="n"/>
     </row>
     <row r="90">
-      <c r="P90" s="6" t="n"/>
+      <c r="P90" s="5" t="n"/>
     </row>
     <row r="91">
-      <c r="P91" s="6" t="n"/>
+      <c r="P91" s="5" t="n"/>
     </row>
     <row r="92">
-      <c r="P92" s="6" t="n"/>
+      <c r="P92" s="5" t="n"/>
     </row>
     <row r="93">
-      <c r="P93" s="6" t="n"/>
+      <c r="P93" s="5" t="n"/>
     </row>
     <row r="94">
-      <c r="P94" s="6" t="n"/>
+      <c r="P94" s="5" t="n"/>
     </row>
     <row r="95">
-      <c r="P95" s="6" t="n"/>
+      <c r="P95" s="5" t="n"/>
     </row>
     <row r="96">
-      <c r="P96" s="6" t="n"/>
+      <c r="P96" s="5" t="n"/>
     </row>
     <row r="97">
-      <c r="P97" s="6" t="n"/>
+      <c r="P97" s="5" t="n"/>
     </row>
     <row r="98">
-      <c r="P98" s="6" t="n"/>
+      <c r="P98" s="5" t="n"/>
     </row>
     <row r="99">
-      <c r="P99" s="6" t="n"/>
+      <c r="P99" s="5" t="n"/>
     </row>
     <row r="100">
-      <c r="P100" s="6" t="n"/>
+      <c r="P100" s="5" t="n"/>
     </row>
     <row r="101">
-      <c r="P101" s="6" t="n"/>
+      <c r="P101" s="5" t="n"/>
     </row>
     <row r="102">
-      <c r="P102" s="6" t="n"/>
+      <c r="P102" s="5" t="n"/>
     </row>
     <row r="103">
-      <c r="P103" s="6" t="n"/>
+      <c r="P103" s="5" t="n"/>
     </row>
     <row r="104">
-      <c r="P104" s="6" t="n"/>
+      <c r="P104" s="5" t="n"/>
     </row>
     <row r="105">
-      <c r="P105" s="6" t="n"/>
+      <c r="P105" s="5" t="n"/>
     </row>
     <row r="106">
-      <c r="P106" s="6" t="n"/>
+      <c r="P106" s="5" t="n"/>
     </row>
     <row r="107">
-      <c r="P107" s="6" t="n"/>
+      <c r="P107" s="5" t="n"/>
     </row>
     <row r="108">
-      <c r="P108" s="6" t="n"/>
+      <c r="P108" s="5" t="n"/>
     </row>
     <row r="109">
-      <c r="P109" s="6" t="n"/>
+      <c r="P109" s="5" t="n"/>
     </row>
     <row r="110">
-      <c r="P110" s="6" t="n"/>
+      <c r="P110" s="5" t="n"/>
     </row>
     <row r="111">
-      <c r="P111" s="6" t="n"/>
+      <c r="P111" s="5" t="n"/>
     </row>
     <row r="112">
-      <c r="P112" s="6" t="n"/>
+      <c r="P112" s="5" t="n"/>
     </row>
     <row r="113">
-      <c r="P113" s="6" t="n"/>
+      <c r="P113" s="5" t="n"/>
     </row>
     <row r="114">
-      <c r="P114" s="6" t="n"/>
+      <c r="P114" s="5" t="n"/>
     </row>
     <row r="115">
-      <c r="P115" s="6" t="n"/>
+      <c r="P115" s="5" t="n"/>
     </row>
     <row r="116">
-      <c r="P116" s="6" t="n"/>
+      <c r="P116" s="5" t="n"/>
     </row>
     <row r="117">
-      <c r="P117" s="6" t="n"/>
+      <c r="P117" s="5" t="n"/>
     </row>
     <row r="118">
-      <c r="P118" s="6" t="n"/>
+      <c r="P118" s="5" t="n"/>
     </row>
     <row r="119">
-      <c r="P119" s="6" t="n"/>
+      <c r="P119" s="5" t="n"/>
     </row>
     <row r="120">
-      <c r="P120" s="6" t="n"/>
+      <c r="P120" s="5" t="n"/>
     </row>
     <row r="121">
-      <c r="P121" s="6" t="n"/>
+      <c r="P121" s="5" t="n"/>
     </row>
     <row r="122">
-      <c r="P122" s="6" t="n"/>
+      <c r="P122" s="5" t="n"/>
     </row>
     <row r="123">
-      <c r="P123" s="6" t="n"/>
+      <c r="P123" s="5" t="n"/>
     </row>
     <row r="124">
-      <c r="P124" s="6" t="n"/>
+      <c r="P124" s="5" t="n"/>
     </row>
     <row r="125">
-      <c r="P125" s="6" t="n"/>
+      <c r="P125" s="5" t="n"/>
     </row>
     <row r="126">
-      <c r="P126" s="6" t="n"/>
+      <c r="P126" s="5" t="n"/>
     </row>
     <row r="127">
-      <c r="P127" s="6" t="n"/>
+      <c r="P127" s="5" t="n"/>
     </row>
     <row r="128">
-      <c r="P128" s="6" t="n"/>
+      <c r="P128" s="5" t="n"/>
     </row>
     <row r="129">
-      <c r="P129" s="6" t="n"/>
+      <c r="P129" s="5" t="n"/>
     </row>
     <row r="130">
-      <c r="P130" s="6" t="n"/>
+      <c r="P130" s="5" t="n"/>
     </row>
     <row r="131">
-      <c r="P131" s="6" t="n"/>
+      <c r="P131" s="5" t="n"/>
     </row>
     <row r="132">
-      <c r="P132" s="6" t="n"/>
+      <c r="P132" s="5" t="n"/>
     </row>
     <row r="133">
-      <c r="P133" s="6" t="n"/>
+      <c r="P133" s="5" t="n"/>
     </row>
     <row r="134">
-      <c r="P134" s="6" t="n"/>
+      <c r="P134" s="5" t="n"/>
     </row>
     <row r="135">
-      <c r="P135" s="6" t="n"/>
+      <c r="P135" s="5" t="n"/>
     </row>
     <row r="136">
-      <c r="P136" s="6" t="n"/>
+      <c r="P136" s="5" t="n"/>
     </row>
     <row r="137">
-      <c r="P137" s="6" t="n"/>
+      <c r="P137" s="5" t="n"/>
     </row>
     <row r="138">
-      <c r="P138" s="6" t="n"/>
+      <c r="P138" s="5" t="n"/>
     </row>
     <row r="139">
-      <c r="P139" s="6" t="n"/>
+      <c r="P139" s="5" t="n"/>
     </row>
     <row r="140">
-      <c r="P140" s="6" t="n"/>
+      <c r="P140" s="5" t="n"/>
     </row>
     <row r="141">
-      <c r="P141" s="6" t="n"/>
+      <c r="P141" s="5" t="n"/>
     </row>
     <row r="142">
-      <c r="P142" s="6" t="n"/>
+      <c r="P142" s="5" t="n"/>
     </row>
     <row r="143">
-      <c r="P143" s="6" t="n"/>
+      <c r="P143" s="5" t="n"/>
     </row>
     <row r="144">
-      <c r="P144" s="6" t="n"/>
+      <c r="P144" s="5" t="n"/>
     </row>
     <row r="145">
-      <c r="P145" s="6" t="n"/>
+      <c r="P145" s="5" t="n"/>
     </row>
     <row r="146">
-      <c r="P146" s="6" t="n"/>
+      <c r="P146" s="5" t="n"/>
     </row>
     <row r="147">
-      <c r="P147" s="6" t="n"/>
+      <c r="P147" s="5" t="n"/>
     </row>
     <row r="148">
-      <c r="P148" s="6" t="n"/>
+      <c r="P148" s="5" t="n"/>
     </row>
     <row r="149">
-      <c r="P149" s="6" t="n"/>
+      <c r="P149" s="5" t="n"/>
     </row>
     <row r="150">
-      <c r="P150" s="6" t="n"/>
+      <c r="P150" s="5" t="n"/>
     </row>
     <row r="151">
-      <c r="P151" s="6" t="n"/>
+      <c r="P151" s="5" t="n"/>
     </row>
     <row r="152">
-      <c r="P152" s="6" t="n"/>
+      <c r="P152" s="5" t="n"/>
     </row>
     <row r="153">
-      <c r="P153" s="6" t="n"/>
+      <c r="P153" s="5" t="n"/>
     </row>
     <row r="154">
-      <c r="P154" s="6" t="n"/>
+      <c r="P154" s="5" t="n"/>
     </row>
     <row r="155">
-      <c r="P155" s="6" t="n"/>
+      <c r="P155" s="5" t="n"/>
     </row>
     <row r="156">
-      <c r="P156" s="6" t="n"/>
+      <c r="P156" s="5" t="n"/>
     </row>
     <row r="157">
-      <c r="P157" s="6" t="n"/>
+      <c r="P157" s="5" t="n"/>
     </row>
     <row r="158">
-      <c r="P158" s="6" t="n"/>
+      <c r="P158" s="5" t="n"/>
     </row>
     <row r="159">
-      <c r="P159" s="6" t="n"/>
+      <c r="P159" s="5" t="n"/>
     </row>
     <row r="160">
-      <c r="P160" s="6" t="n"/>
+      <c r="P160" s="5" t="n"/>
     </row>
     <row r="161">
-      <c r="P161" s="6" t="n"/>
+      <c r="P161" s="5" t="n"/>
     </row>
     <row r="162">
-      <c r="P162" s="6" t="n"/>
+      <c r="P162" s="5" t="n"/>
     </row>
     <row r="163">
-      <c r="P163" s="6" t="n"/>
+      <c r="P163" s="5" t="n"/>
     </row>
     <row r="164">
-      <c r="P164" s="6" t="n"/>
+      <c r="P164" s="5" t="n"/>
     </row>
     <row r="165">
-      <c r="P165" s="6" t="n"/>
+      <c r="P165" s="5" t="n"/>
     </row>
     <row r="166">
-      <c r="P166" s="6" t="n"/>
+      <c r="P166" s="5" t="n"/>
     </row>
     <row r="167">
-      <c r="P167" s="6" t="n"/>
+      <c r="P167" s="5" t="n"/>
     </row>
     <row r="168">
-      <c r="P168" s="6" t="n"/>
+      <c r="P168" s="5" t="n"/>
     </row>
     <row r="169">
-      <c r="P169" s="6" t="n"/>
+      <c r="P169" s="5" t="n"/>
     </row>
     <row r="170">
-      <c r="P170" s="6" t="n"/>
+      <c r="P170" s="5" t="n"/>
     </row>
     <row r="171">
-      <c r="P171" s="6" t="n"/>
+      <c r="P171" s="5" t="n"/>
     </row>
     <row r="172">
-      <c r="P172" s="6" t="n"/>
+      <c r="P172" s="5" t="n"/>
     </row>
     <row r="173">
-      <c r="P173" s="6" t="n"/>
+      <c r="P173" s="5" t="n"/>
     </row>
     <row r="174">
-      <c r="P174" s="6" t="n"/>
+      <c r="P174" s="5" t="n"/>
     </row>
     <row r="175">
-      <c r="P175" s="6" t="n"/>
+      <c r="P175" s="5" t="n"/>
     </row>
     <row r="176">
-      <c r="P176" s="6" t="n"/>
+      <c r="P176" s="5" t="n"/>
     </row>
     <row r="177">
-      <c r="P177" s="6" t="n"/>
+      <c r="P177" s="5" t="n"/>
     </row>
     <row r="178">
-      <c r="P178" s="6" t="n"/>
+      <c r="P178" s="5" t="n"/>
     </row>
     <row r="179">
-      <c r="P179" s="6" t="n"/>
+      <c r="P179" s="5" t="n"/>
     </row>
     <row r="180">
-      <c r="P180" s="6" t="n"/>
+      <c r="P180" s="5" t="n"/>
     </row>
     <row r="181">
-      <c r="P181" s="6" t="n"/>
+      <c r="P181" s="5" t="n"/>
     </row>
     <row r="182">
-      <c r="P182" s="6" t="n"/>
+      <c r="P182" s="5" t="n"/>
     </row>
     <row r="183">
-      <c r="P183" s="6" t="n"/>
+      <c r="P183" s="5" t="n"/>
     </row>
     <row r="184">
-      <c r="P184" s="6" t="n"/>
+      <c r="P184" s="5" t="n"/>
     </row>
     <row r="185">
-      <c r="P185" s="6" t="n"/>
+      <c r="P185" s="5" t="n"/>
     </row>
     <row r="186">
-      <c r="P186" s="6" t="n"/>
+      <c r="P186" s="5" t="n"/>
     </row>
     <row r="187">
-      <c r="P187" s="6" t="n"/>
+      <c r="P187" s="5" t="n"/>
     </row>
     <row r="188">
-      <c r="P188" s="6" t="n"/>
+      <c r="P188" s="5" t="n"/>
     </row>
     <row r="189">
-      <c r="P189" s="6" t="n"/>
+      <c r="P189" s="5" t="n"/>
     </row>
     <row r="190">
-      <c r="P190" s="6" t="n"/>
+      <c r="P190" s="5" t="n"/>
     </row>
     <row r="191">
-      <c r="P191" s="6" t="n"/>
+      <c r="P191" s="5" t="n"/>
     </row>
     <row r="192">
-      <c r="P192" s="6" t="n"/>
+      <c r="P192" s="5" t="n"/>
     </row>
     <row r="193">
-      <c r="P193" s="6" t="n"/>
+      <c r="P193" s="5" t="n"/>
     </row>
     <row r="194">
-      <c r="P194" s="6" t="n"/>
+      <c r="P194" s="5" t="n"/>
     </row>
     <row r="195">
-      <c r="P195" s="6" t="n"/>
+      <c r="P195" s="5" t="n"/>
     </row>
     <row r="196">
-      <c r="P196" s="6" t="n"/>
+      <c r="P196" s="5" t="n"/>
     </row>
     <row r="197">
-      <c r="P197" s="6" t="n"/>
+      <c r="P197" s="5" t="n"/>
     </row>
     <row r="198">
-      <c r="P198" s="6" t="n"/>
+      <c r="P198" s="5" t="n"/>
     </row>
     <row r="199">
-      <c r="P199" s="6" t="n"/>
+      <c r="P199" s="5" t="n"/>
     </row>
     <row r="200">
-      <c r="P200" s="6" t="n"/>
+      <c r="P200" s="5" t="n"/>
     </row>
     <row r="201">
-      <c r="P201" s="6" t="n"/>
+      <c r="P201" s="5" t="n"/>
     </row>
     <row r="202">
-      <c r="P202" s="6" t="n"/>
+      <c r="P202" s="5" t="n"/>
     </row>
     <row r="203">
-      <c r="P203" s="6" t="n"/>
+      <c r="P203" s="5" t="n"/>
     </row>
     <row r="204">
-      <c r="P204" s="6" t="n"/>
+      <c r="P204" s="5" t="n"/>
     </row>
     <row r="205">
-      <c r="P205" s="6" t="n"/>
+      <c r="P205" s="5" t="n"/>
     </row>
     <row r="206">
-      <c r="P206" s="6" t="n"/>
+      <c r="P206" s="5" t="n"/>
     </row>
     <row r="207">
-      <c r="P207" s="6" t="n"/>
+      <c r="P207" s="5" t="n"/>
     </row>
     <row r="208">
-      <c r="P208" s="6" t="n"/>
+      <c r="P208" s="5" t="n"/>
     </row>
     <row r="209">
-      <c r="P209" s="6" t="n"/>
+      <c r="P209" s="5" t="n"/>
     </row>
     <row r="210">
-      <c r="P210" s="6" t="n"/>
+      <c r="P210" s="5" t="n"/>
     </row>
     <row r="211">
-      <c r="P211" s="6" t="n"/>
+      <c r="P211" s="5" t="n"/>
     </row>
     <row r="212">
-      <c r="P212" s="6" t="n"/>
+      <c r="P212" s="5" t="n"/>
     </row>
     <row r="213">
-      <c r="P213" s="6" t="n"/>
+      <c r="P213" s="5" t="n"/>
     </row>
     <row r="214">
-      <c r="P214" s="6" t="n"/>
+      <c r="P214" s="5" t="n"/>
     </row>
     <row r="215">
-      <c r="P215" s="6" t="n"/>
+      <c r="P215" s="5" t="n"/>
     </row>
     <row r="216">
-      <c r="P216" s="6" t="n"/>
+      <c r="P216" s="5" t="n"/>
     </row>
     <row r="217">
-      <c r="P217" s="6" t="n"/>
+      <c r="P217" s="5" t="n"/>
     </row>
     <row r="218">
-      <c r="P218" s="6" t="n"/>
+      <c r="P218" s="5" t="n"/>
     </row>
     <row r="219">
-      <c r="P219" s="6" t="n"/>
+      <c r="P219" s="5" t="n"/>
     </row>
     <row r="220">
-      <c r="P220" s="6" t="n"/>
+      <c r="P220" s="5" t="n"/>
     </row>
     <row r="221">
-      <c r="P221" s="6" t="n"/>
+      <c r="P221" s="5" t="n"/>
     </row>
     <row r="222">
-      <c r="P222" s="6" t="n"/>
+      <c r="P222" s="5" t="n"/>
     </row>
     <row r="223">
-      <c r="P223" s="6" t="n"/>
+      <c r="P223" s="5" t="n"/>
     </row>
     <row r="224">
-      <c r="P224" s="6" t="n"/>
+      <c r="P224" s="5" t="n"/>
     </row>
     <row r="225">
-      <c r="P225" s="6" t="n"/>
+      <c r="P225" s="5" t="n"/>
     </row>
     <row r="226">
-      <c r="P226" s="6" t="n"/>
+      <c r="P226" s="5" t="n"/>
     </row>
     <row r="227">
-      <c r="P227" s="6" t="n"/>
+      <c r="P227" s="5" t="n"/>
     </row>
     <row r="228">
-      <c r="P228" s="6" t="n"/>
+      <c r="P228" s="5" t="n"/>
     </row>
     <row r="229">
-      <c r="P229" s="6" t="n"/>
+      <c r="P229" s="5" t="n"/>
     </row>
     <row r="230">
-      <c r="P230" s="6" t="n"/>
+      <c r="P230" s="5" t="n"/>
     </row>
     <row r="231">
-      <c r="P231" s="6" t="n"/>
+      <c r="P231" s="5" t="n"/>
     </row>
     <row r="232">
-      <c r="P232" s="6" t="n"/>
+      <c r="P232" s="5" t="n"/>
     </row>
     <row r="233">
-      <c r="P233" s="6" t="n"/>
+      <c r="P233" s="5" t="n"/>
     </row>
     <row r="234">
-      <c r="P234" s="6" t="n"/>
+      <c r="P234" s="5" t="n"/>
     </row>
     <row r="235">
-      <c r="P235" s="6" t="n"/>
+      <c r="P235" s="5" t="n"/>
     </row>
     <row r="236">
-      <c r="P236" s="6" t="n"/>
+      <c r="P236" s="5" t="n"/>
     </row>
     <row r="237">
-      <c r="P237" s="6" t="n"/>
+      <c r="P237" s="5" t="n"/>
     </row>
     <row r="238">
-      <c r="P238" s="6" t="n"/>
+      <c r="P238" s="5" t="n"/>
     </row>
     <row r="239">
-      <c r="P239" s="6" t="n"/>
+      <c r="P239" s="5" t="n"/>
     </row>
     <row r="240">
-      <c r="P240" s="6" t="n"/>
+      <c r="P240" s="5" t="n"/>
     </row>
     <row r="241">
-      <c r="P241" s="6" t="n"/>
+      <c r="P241" s="5" t="n"/>
     </row>
     <row r="242">
-      <c r="P242" s="6" t="n"/>
+      <c r="P242" s="5" t="n"/>
     </row>
     <row r="243">
-      <c r="P243" s="6" t="n"/>
+      <c r="P243" s="5" t="n"/>
     </row>
     <row r="244">
-      <c r="P244" s="6" t="n"/>
+      <c r="P244" s="5" t="n"/>
     </row>
     <row r="245">
-      <c r="P245" s="6" t="n"/>
+      <c r="P245" s="5" t="n"/>
     </row>
     <row r="246">
-      <c r="P246" s="6" t="n"/>
+      <c r="P246" s="5" t="n"/>
     </row>
     <row r="247">
-      <c r="P247" s="6" t="n"/>
+      <c r="P247" s="5" t="n"/>
     </row>
     <row r="248">
-      <c r="P248" s="6" t="n"/>
+      <c r="P248" s="5" t="n"/>
     </row>
     <row r="249">
-      <c r="P249" s="6" t="n"/>
+      <c r="P249" s="5" t="n"/>
     </row>
     <row r="250">
-      <c r="P250" s="6" t="n"/>
+      <c r="P250" s="5" t="n"/>
     </row>
     <row r="251">
-      <c r="P251" s="6" t="n"/>
+      <c r="P251" s="5" t="n"/>
     </row>
     <row r="252">
-      <c r="P252" s="6" t="n"/>
+      <c r="P252" s="5" t="n"/>
     </row>
     <row r="253">
-      <c r="P253" s="6" t="n"/>
+      <c r="P253" s="5" t="n"/>
     </row>
     <row r="254">
-      <c r="P254" s="6" t="n"/>
+      <c r="P254" s="5" t="n"/>
     </row>
     <row r="255">
-      <c r="P255" s="6" t="n"/>
+      <c r="P255" s="5" t="n"/>
     </row>
     <row r="256">
-      <c r="P256" s="6" t="n"/>
+      <c r="P256" s="5" t="n"/>
     </row>
     <row r="257">
-      <c r="P257" s="6" t="n"/>
+      <c r="P257" s="5" t="n"/>
     </row>
     <row r="258">
-      <c r="P258" s="6" t="n"/>
+      <c r="P258" s="5" t="n"/>
     </row>
     <row r="259">
-      <c r="P259" s="6" t="n"/>
+      <c r="P259" s="5" t="n"/>
     </row>
     <row r="260">
-      <c r="P260" s="6" t="n"/>
+      <c r="P260" s="5" t="n"/>
     </row>
     <row r="261">
-      <c r="P261" s="6" t="n"/>
+      <c r="P261" s="5" t="n"/>
     </row>
     <row r="262">
-      <c r="P262" s="6" t="n"/>
+      <c r="P262" s="5" t="n"/>
     </row>
     <row r="263">
-      <c r="P263" s="6" t="n"/>
+      <c r="P263" s="5" t="n"/>
     </row>
     <row r="264">
-      <c r="P264" s="6" t="n"/>
+      <c r="P264" s="5" t="n"/>
     </row>
     <row r="265">
-      <c r="P265" s="6" t="n"/>
+      <c r="P265" s="5" t="n"/>
     </row>
     <row r="266">
-      <c r="P266" s="6" t="n"/>
+      <c r="P266" s="5" t="n"/>
     </row>
     <row r="267">
-      <c r="P267" s="6" t="n"/>
+      <c r="P267" s="5" t="n"/>
     </row>
     <row r="268">
-      <c r="P268" s="6" t="n"/>
+      <c r="P268" s="5" t="n"/>
     </row>
     <row r="269">
-      <c r="P269" s="6" t="n"/>
+      <c r="P269" s="5" t="n"/>
     </row>
     <row r="270">
-      <c r="P270" s="6" t="n"/>
+      <c r="P270" s="5" t="n"/>
     </row>
     <row r="271">
-      <c r="P271" s="6" t="n"/>
+      <c r="P271" s="5" t="n"/>
     </row>
     <row r="272">
-      <c r="P272" s="6" t="n"/>
+      <c r="P272" s="5" t="n"/>
     </row>
     <row r="273">
-      <c r="P273" s="6" t="n"/>
+      <c r="P273" s="5" t="n"/>
     </row>
     <row r="274">
-      <c r="P274" s="6" t="n"/>
+      <c r="P274" s="5" t="n"/>
     </row>
     <row r="275">
-      <c r="P275" s="6" t="n"/>
+      <c r="P275" s="5" t="n"/>
     </row>
     <row r="276">
-      <c r="P276" s="6" t="n"/>
+      <c r="P276" s="5" t="n"/>
     </row>
     <row r="277">
-      <c r="P277" s="6" t="n"/>
+      <c r="P277" s="5" t="n"/>
     </row>
     <row r="278">
-      <c r="P278" s="6" t="n"/>
+      <c r="P278" s="5" t="n"/>
     </row>
     <row r="279">
-      <c r="P279" s="6" t="n"/>
+      <c r="P279" s="5" t="n"/>
     </row>
     <row r="280">
-      <c r="P280" s="6" t="n"/>
+      <c r="P280" s="5" t="n"/>
     </row>
     <row r="281">
-      <c r="P281" s="6" t="n"/>
+      <c r="P281" s="5" t="n"/>
     </row>
     <row r="282">
-      <c r="P282" s="6" t="n"/>
+      <c r="P282" s="5" t="n"/>
     </row>
     <row r="283">
-      <c r="P283" s="6" t="n"/>
+      <c r="P283" s="5" t="n"/>
     </row>
     <row r="284">
-      <c r="P284" s="6" t="n"/>
+      <c r="P284" s="5" t="n"/>
     </row>
     <row r="285">
-      <c r="P285" s="6" t="n"/>
+      <c r="P285" s="5" t="n"/>
     </row>
     <row r="286">
-      <c r="P286" s="6" t="n"/>
+      <c r="P286" s="5" t="n"/>
     </row>
     <row r="287">
-      <c r="P287" s="6" t="n"/>
+      <c r="P287" s="5" t="n"/>
     </row>
     <row r="288">
-      <c r="P288" s="6" t="n"/>
+      <c r="P288" s="5" t="n"/>
     </row>
     <row r="289">
-      <c r="P289" s="6" t="n"/>
+      <c r="P289" s="5" t="n"/>
     </row>
     <row r="290">
-      <c r="P290" s="6" t="n"/>
+      <c r="P290" s="5" t="n"/>
     </row>
     <row r="291">
-      <c r="P291" s="6" t="n"/>
+      <c r="P291" s="5" t="n"/>
     </row>
     <row r="292">
-      <c r="P292" s="6" t="n"/>
+      <c r="P292" s="5" t="n"/>
     </row>
     <row r="293">
-      <c r="P293" s="6" t="n"/>
+      <c r="P293" s="5" t="n"/>
     </row>
     <row r="294">
-      <c r="P294" s="6" t="n"/>
+      <c r="P294" s="5" t="n"/>
     </row>
     <row r="295">
-      <c r="P295" s="6" t="n"/>
+      <c r="P295" s="5" t="n"/>
     </row>
     <row r="296">
-      <c r="P296" s="6" t="n"/>
+      <c r="P296" s="5" t="n"/>
     </row>
     <row r="297">
-      <c r="P297" s="6" t="n"/>
+      <c r="P297" s="5" t="n"/>
     </row>
     <row r="298">
-      <c r="P298" s="6" t="n"/>
+      <c r="P298" s="5" t="n"/>
     </row>
     <row r="299">
-      <c r="P299" s="6" t="n"/>
+      <c r="P299" s="5" t="n"/>
     </row>
     <row r="300">
-      <c r="P300" s="6" t="n"/>
+      <c r="P300" s="5" t="n"/>
     </row>
     <row r="301">
-      <c r="P301" s="6" t="n"/>
+      <c r="P301" s="5" t="n"/>
     </row>
     <row r="302">
-      <c r="P302" s="6" t="n"/>
+      <c r="P302" s="5" t="n"/>
     </row>
     <row r="303">
-      <c r="P303" s="6" t="n"/>
+      <c r="P303" s="5" t="n"/>
     </row>
     <row r="304">
-      <c r="P304" s="6" t="n"/>
+      <c r="P304" s="5" t="n"/>
     </row>
     <row r="305">
-      <c r="P305" s="6" t="n"/>
+      <c r="P305" s="5" t="n"/>
     </row>
     <row r="306">
-      <c r="P306" s="6" t="n"/>
+      <c r="P306" s="5" t="n"/>
     </row>
     <row r="307">
-      <c r="P307" s="6" t="n"/>
+      <c r="P307" s="5" t="n"/>
     </row>
     <row r="308">
-      <c r="P308" s="6" t="n"/>
+      <c r="P308" s="5" t="n"/>
     </row>
     <row r="309">
-      <c r="P309" s="6" t="n"/>
+      <c r="P309" s="5" t="n"/>
     </row>
     <row r="310">
-      <c r="P310" s="6" t="n"/>
+      <c r="P310" s="5" t="n"/>
     </row>
     <row r="311">
-      <c r="P311" s="6" t="n"/>
+      <c r="P311" s="5" t="n"/>
     </row>
     <row r="312">
-      <c r="P312" s="6" t="n"/>
+      <c r="P312" s="5" t="n"/>
     </row>
     <row r="313">
-      <c r="P313" s="6" t="n"/>
+      <c r="P313" s="5" t="n"/>
     </row>
     <row r="314">
-      <c r="P314" s="6" t="n"/>
+      <c r="P314" s="5" t="n"/>
     </row>
     <row r="315">
-      <c r="P315" s="6" t="n"/>
+      <c r="P315" s="5" t="n"/>
     </row>
     <row r="316">
-      <c r="P316" s="6" t="n"/>
+      <c r="P316" s="5" t="n"/>
     </row>
     <row r="317">
-      <c r="P317" s="6" t="n"/>
+      <c r="P317" s="5" t="n"/>
     </row>
     <row r="318">
-      <c r="P318" s="6" t="n"/>
+      <c r="P318" s="5" t="n"/>
     </row>
     <row r="319">
-      <c r="P319" s="6" t="n"/>
+      <c r="P319" s="5" t="n"/>
     </row>
     <row r="320">
-      <c r="P320" s="6" t="n"/>
+      <c r="P320" s="5" t="n"/>
     </row>
     <row r="321">
-      <c r="P321" s="6" t="n"/>
+      <c r="P321" s="5" t="n"/>
     </row>
     <row r="322">
-      <c r="P322" s="6" t="n"/>
+      <c r="P322" s="5" t="n"/>
     </row>
     <row r="323">
-      <c r="P323" s="6" t="n"/>
+      <c r="P323" s="5" t="n"/>
     </row>
     <row r="324">
-      <c r="P324" s="6" t="n"/>
+      <c r="P324" s="5" t="n"/>
     </row>
     <row r="325">
-      <c r="P325" s="6" t="n"/>
+      <c r="P325" s="5" t="n"/>
     </row>
     <row r="326">
-      <c r="P326" s="6" t="n"/>
+      <c r="P326" s="5" t="n"/>
     </row>
     <row r="327">
-      <c r="P327" s="6" t="n"/>
+      <c r="P327" s="5" t="n"/>
     </row>
     <row r="328">
-      <c r="P328" s="6" t="n"/>
+      <c r="P328" s="5" t="n"/>
     </row>
     <row r="329">
-      <c r="P329" s="6" t="n"/>
+      <c r="P329" s="5" t="n"/>
     </row>
     <row r="330">
-      <c r="P330" s="6" t="n"/>
+      <c r="P330" s="5" t="n"/>
     </row>
     <row r="331">
-      <c r="P331" s="6" t="n"/>
+      <c r="P331" s="5" t="n"/>
     </row>
     <row r="332">
-      <c r="P332" s="6" t="n"/>
+      <c r="P332" s="5" t="n"/>
     </row>
     <row r="333">
-      <c r="P333" s="6" t="n"/>
+      <c r="P333" s="5" t="n"/>
     </row>
     <row r="334">
-      <c r="P334" s="6" t="n"/>
+      <c r="P334" s="5" t="n"/>
     </row>
     <row r="335">
-      <c r="P335" s="6" t="n"/>
+      <c r="P335" s="5" t="n"/>
     </row>
     <row r="336">
-      <c r="P336" s="6" t="n"/>
+      <c r="P336" s="5" t="n"/>
     </row>
     <row r="337">
-      <c r="P337" s="6" t="n"/>
+      <c r="P337" s="5" t="n"/>
     </row>
     <row r="338">
-      <c r="P338" s="6" t="n"/>
+      <c r="P338" s="5" t="n"/>
     </row>
     <row r="339">
-      <c r="P339" s="6" t="n"/>
+      <c r="P339" s="5" t="n"/>
     </row>
     <row r="340">
-      <c r="P340" s="6" t="n"/>
+      <c r="P340" s="5" t="n"/>
     </row>
     <row r="341">
-      <c r="P341" s="6" t="n"/>
+      <c r="P341" s="5" t="n"/>
     </row>
     <row r="342">
-      <c r="P342" s="6" t="n"/>
+      <c r="P342" s="5" t="n"/>
     </row>
     <row r="343">
-      <c r="P343" s="6" t="n"/>
+      <c r="P343" s="5" t="n"/>
     </row>
     <row r="344">
-      <c r="P344" s="6" t="n"/>
+      <c r="P344" s="5" t="n"/>
     </row>
     <row r="345">
-      <c r="P345" s="6" t="n"/>
+      <c r="P345" s="5" t="n"/>
     </row>
     <row r="346">
-      <c r="P346" s="6" t="n"/>
+      <c r="P346" s="5" t="n"/>
     </row>
     <row r="347">
-      <c r="P347" s="6" t="n"/>
+      <c r="P347" s="5" t="n"/>
     </row>
     <row r="348">
-      <c r="P348" s="6" t="n"/>
+      <c r="P348" s="5" t="n"/>
     </row>
     <row r="349">
-      <c r="P349" s="6" t="n"/>
+      <c r="P349" s="5" t="n"/>
     </row>
     <row r="350">
-      <c r="P350" s="6" t="n"/>
+      <c r="P350" s="5" t="n"/>
     </row>
     <row r="351">
-      <c r="P351" s="6" t="n"/>
+      <c r="P351" s="5" t="n"/>
     </row>
     <row r="352">
-      <c r="P352" s="6" t="n"/>
+      <c r="P352" s="5" t="n"/>
     </row>
     <row r="353">
-      <c r="P353" s="6" t="n"/>
+      <c r="P353" s="5" t="n"/>
     </row>
     <row r="354">
-      <c r="P354" s="6" t="n"/>
+      <c r="P354" s="5" t="n"/>
     </row>
     <row r="355">
-      <c r="P355" s="6" t="n"/>
+      <c r="P355" s="5" t="n"/>
     </row>
     <row r="356">
-      <c r="P356" s="6" t="n"/>
+      <c r="P356" s="5" t="n"/>
     </row>
     <row r="357">
-      <c r="P357" s="6" t="n"/>
+      <c r="P357" s="5" t="n"/>
     </row>
     <row r="358">
-      <c r="P358" s="6" t="n"/>
+      <c r="P358" s="5" t="n"/>
     </row>
     <row r="359">
-      <c r="P359" s="6" t="n"/>
+      <c r="P359" s="5" t="n"/>
     </row>
     <row r="360">
-      <c r="P360" s="6" t="n"/>
+      <c r="P360" s="5" t="n"/>
     </row>
     <row r="361">
-      <c r="P361" s="6" t="n"/>
+      <c r="P361" s="5" t="n"/>
     </row>
     <row r="362">
-      <c r="P362" s="6" t="n"/>
+      <c r="P362" s="5" t="n"/>
     </row>
     <row r="363">
-      <c r="P363" s="6" t="n"/>
+      <c r="P363" s="5" t="n"/>
     </row>
     <row r="364">
-      <c r="P364" s="6" t="n"/>
+      <c r="P364" s="5" t="n"/>
     </row>
     <row r="365">
-      <c r="P365" s="6" t="n"/>
+      <c r="P365" s="5" t="n"/>
     </row>
     <row r="366">
-      <c r="P366" s="6" t="n"/>
+      <c r="P366" s="5" t="n"/>
     </row>
     <row r="367">
-      <c r="P367" s="6" t="n"/>
+      <c r="P367" s="5" t="n"/>
     </row>
     <row r="368">
-      <c r="P368" s="6" t="n"/>
+      <c r="P368" s="5" t="n"/>
     </row>
     <row r="369">
-      <c r="P369" s="6" t="n"/>
+      <c r="P369" s="5" t="n"/>
     </row>
     <row r="370">
-      <c r="P370" s="6" t="n"/>
+      <c r="P370" s="5" t="n"/>
     </row>
     <row r="371">
-      <c r="P371" s="6" t="n"/>
+      <c r="P371" s="5" t="n"/>
     </row>
     <row r="372">
-      <c r="P372" s="6" t="n"/>
+      <c r="P372" s="5" t="n"/>
     </row>
     <row r="373">
-      <c r="P373" s="6" t="n"/>
+      <c r="P373" s="5" t="n"/>
     </row>
     <row r="374">
-      <c r="P374" s="6" t="n"/>
+      <c r="P374" s="5" t="n"/>
     </row>
     <row r="375">
-      <c r="P375" s="6" t="n"/>
+      <c r="P375" s="5" t="n"/>
     </row>
     <row r="376">
-      <c r="P376" s="6" t="n"/>
+      <c r="P376" s="5" t="n"/>
     </row>
     <row r="377">
-      <c r="P377" s="6" t="n"/>
+      <c r="P377" s="5" t="n"/>
     </row>
     <row r="378">
-      <c r="P378" s="6" t="n"/>
+      <c r="P378" s="5" t="n"/>
     </row>
     <row r="379">
-      <c r="P379" s="6" t="n"/>
+      <c r="P379" s="5" t="n"/>
     </row>
     <row r="380">
-      <c r="P380" s="6" t="n"/>
+      <c r="P380" s="5" t="n"/>
     </row>
     <row r="381">
-      <c r="P381" s="6" t="n"/>
+      <c r="P381" s="5" t="n"/>
     </row>
     <row r="382">
-      <c r="P382" s="6" t="n"/>
+      <c r="P382" s="5" t="n"/>
     </row>
     <row r="383">
-      <c r="P383" s="6" t="n"/>
+      <c r="P383" s="5" t="n"/>
     </row>
     <row r="384">
-      <c r="P384" s="6" t="n"/>
+      <c r="P384" s="5" t="n"/>
     </row>
     <row r="385">
-      <c r="P385" s="6" t="n"/>
+      <c r="P385" s="5" t="n"/>
     </row>
     <row r="386">
-      <c r="P386" s="6" t="n"/>
+      <c r="P386" s="5" t="n"/>
     </row>
     <row r="387">
-      <c r="P387" s="6" t="n"/>
+      <c r="P387" s="5" t="n"/>
     </row>
     <row r="388">
-      <c r="P388" s="6" t="n"/>
+      <c r="P388" s="5" t="n"/>
     </row>
     <row r="389">
-      <c r="P389" s="6" t="n"/>
+      <c r="P389" s="5" t="n"/>
     </row>
     <row r="390">
-      <c r="P390" s="6" t="n"/>
+      <c r="P390" s="5" t="n"/>
     </row>
     <row r="391">
-      <c r="P391" s="6" t="n"/>
+      <c r="P391" s="5" t="n"/>
     </row>
     <row r="392">
-      <c r="P392" s="6" t="n"/>
+      <c r="P392" s="5" t="n"/>
     </row>
     <row r="393">
-      <c r="P393" s="6" t="n"/>
+      <c r="P393" s="5" t="n"/>
     </row>
     <row r="394">
-      <c r="P394" s="6" t="n"/>
+      <c r="P394" s="5" t="n"/>
     </row>
     <row r="395">
-      <c r="P395" s="6" t="n"/>
+      <c r="P395" s="5" t="n"/>
     </row>
     <row r="396">
-      <c r="P396" s="6" t="n"/>
+      <c r="P396" s="5" t="n"/>
     </row>
     <row r="397">
-      <c r="P397" s="6" t="n"/>
+      <c r="P397" s="5" t="n"/>
     </row>
     <row r="398">
-      <c r="P398" s="6" t="n"/>
+      <c r="P398" s="5" t="n"/>
     </row>
     <row r="399">
-      <c r="P399" s="6" t="n"/>
+      <c r="P399" s="5" t="n"/>
     </row>
     <row r="400">
-      <c r="P400" s="6" t="n"/>
+      <c r="P400" s="5" t="n"/>
     </row>
     <row r="401">
-      <c r="P401" s="6" t="n"/>
+      <c r="P401" s="5" t="n"/>
     </row>
     <row r="402">
-      <c r="P402" s="6" t="n"/>
+      <c r="P402" s="5" t="n"/>
     </row>
     <row r="403">
-      <c r="P403" s="6" t="n"/>
+      <c r="P403" s="5" t="n"/>
     </row>
     <row r="404">
-      <c r="P404" s="6" t="n"/>
+      <c r="P404" s="5" t="n"/>
     </row>
     <row r="405">
-      <c r="P405" s="6" t="n"/>
+      <c r="P405" s="5" t="n"/>
     </row>
     <row r="406">
-      <c r="P406" s="6" t="n"/>
+      <c r="P406" s="5" t="n"/>
     </row>
     <row r="407">
-      <c r="P407" s="6" t="n"/>
+      <c r="P407" s="5" t="n"/>
     </row>
     <row r="408">
-      <c r="P408" s="6" t="n"/>
+      <c r="P408" s="5" t="n"/>
     </row>
     <row r="409">
-      <c r="P409" s="6" t="n"/>
+      <c r="P409" s="5" t="n"/>
     </row>
     <row r="410">
-      <c r="P410" s="6" t="n"/>
+      <c r="P410" s="5" t="n"/>
     </row>
     <row r="411">
-      <c r="P411" s="6" t="n"/>
+      <c r="P411" s="5" t="n"/>
     </row>
     <row r="412">
-      <c r="P412" s="6" t="n"/>
+      <c r="P412" s="5" t="n"/>
     </row>
     <row r="413">
-      <c r="P413" s="6" t="n"/>
+      <c r="P413" s="5" t="n"/>
     </row>
     <row r="414">
-      <c r="P414" s="6" t="n"/>
+      <c r="P414" s="5" t="n"/>
     </row>
     <row r="415">
-      <c r="P415" s="6" t="n"/>
+      <c r="P415" s="5" t="n"/>
     </row>
     <row r="416">
-      <c r="P416" s="6" t="n"/>
+      <c r="P416" s="5" t="n"/>
     </row>
     <row r="417">
-      <c r="P417" s="6" t="n"/>
+      <c r="P417" s="5" t="n"/>
     </row>
     <row r="418">
-      <c r="P418" s="6" t="n"/>
+      <c r="P418" s="5" t="n"/>
     </row>
     <row r="419">
-      <c r="P419" s="6" t="n"/>
+      <c r="P419" s="5" t="n"/>
     </row>
     <row r="420">
-      <c r="P420" s="6" t="n"/>
+      <c r="P420" s="5" t="n"/>
     </row>
     <row r="421">
-      <c r="P421" s="6" t="n"/>
+      <c r="P421" s="5" t="n"/>
     </row>
     <row r="422">
-      <c r="P422" s="6" t="n"/>
+      <c r="P422" s="5" t="n"/>
     </row>
     <row r="423">
-      <c r="P423" s="6" t="n"/>
+      <c r="P423" s="5" t="n"/>
     </row>
     <row r="424">
-      <c r="P424" s="6" t="n"/>
+      <c r="P424" s="5" t="n"/>
     </row>
     <row r="425">
-      <c r="P425" s="6" t="n"/>
+      <c r="P425" s="5" t="n"/>
     </row>
     <row r="426">
-      <c r="P426" s="6" t="n"/>
+      <c r="P426" s="5" t="n"/>
     </row>
     <row r="427">
-      <c r="P427" s="6" t="n"/>
+      <c r="P427" s="5" t="n"/>
     </row>
     <row r="428">
-      <c r="P428" s="6" t="n"/>
+      <c r="P428" s="5" t="n"/>
     </row>
     <row r="429">
-      <c r="P429" s="6" t="n"/>
+      <c r="P429" s="5" t="n"/>
     </row>
     <row r="430">
-      <c r="P430" s="6" t="n"/>
+      <c r="P430" s="5" t="n"/>
     </row>
     <row r="431">
-      <c r="P431" s="6" t="n"/>
+      <c r="P431" s="5" t="n"/>
     </row>
     <row r="432">
-      <c r="P432" s="6" t="n"/>
+      <c r="P432" s="5" t="n"/>
     </row>
     <row r="433">
-      <c r="P433" s="6" t="n"/>
+      <c r="P433" s="5" t="n"/>
     </row>
     <row r="434">
-      <c r="P434" s="6" t="n"/>
+      <c r="P434" s="5" t="n"/>
     </row>
     <row r="435">
-      <c r="P435" s="6" t="n"/>
+      <c r="P435" s="5" t="n"/>
     </row>
     <row r="436">
-      <c r="P436" s="6" t="n"/>
+      <c r="P436" s="5" t="n"/>
     </row>
     <row r="437">
-      <c r="P437" s="6" t="n"/>
+      <c r="P437" s="5" t="n"/>
     </row>
     <row r="438">
-      <c r="P438" s="6" t="n"/>
+      <c r="P438" s="5" t="n"/>
     </row>
     <row r="439">
-      <c r="P439" s="6" t="n"/>
+      <c r="P439" s="5" t="n"/>
     </row>
     <row r="440">
-      <c r="P440" s="6" t="n"/>
+      <c r="P440" s="5" t="n"/>
     </row>
     <row r="441">
-      <c r="P441" s="6" t="n"/>
+      <c r="P441" s="5" t="n"/>
     </row>
     <row r="442">
-      <c r="P442" s="6" t="n"/>
+      <c r="P442" s="5" t="n"/>
     </row>
     <row r="443">
-      <c r="P443" s="6" t="n"/>
+      <c r="P443" s="5" t="n"/>
     </row>
     <row r="444">
-      <c r="P444" s="6" t="n"/>
+      <c r="P444" s="5" t="n"/>
     </row>
     <row r="445">
-      <c r="P445" s="6" t="n"/>
+      <c r="P445" s="5" t="n"/>
     </row>
     <row r="446">
-      <c r="P446" s="6" t="n"/>
+      <c r="P446" s="5" t="n"/>
     </row>
     <row r="447">
-      <c r="P447" s="6" t="n"/>
+      <c r="P447" s="5" t="n"/>
     </row>
     <row r="448">
-      <c r="P448" s="6" t="n"/>
+      <c r="P448" s="5" t="n"/>
     </row>
     <row r="449">
-      <c r="P449" s="6" t="n"/>
+      <c r="P449" s="5" t="n"/>
     </row>
     <row r="450">
-      <c r="P450" s="6" t="n"/>
+      <c r="P450" s="5" t="n"/>
     </row>
     <row r="451">
-      <c r="P451" s="6" t="n"/>
+      <c r="P451" s="5" t="n"/>
     </row>
     <row r="452">
-      <c r="P452" s="6" t="n"/>
+      <c r="P452" s="5" t="n"/>
     </row>
     <row r="453">
-      <c r="P453" s="6" t="n"/>
+      <c r="P453" s="5" t="n"/>
     </row>
     <row r="454">
-      <c r="P454" s="6" t="n"/>
+      <c r="P454" s="5" t="n"/>
     </row>
     <row r="455">
-      <c r="P455" s="6" t="n"/>
+      <c r="P455" s="5" t="n"/>
     </row>
     <row r="456">
-      <c r="P456" s="6" t="n"/>
+      <c r="P456" s="5" t="n"/>
     </row>
     <row r="457">
-      <c r="P457" s="6" t="n"/>
+      <c r="P457" s="5" t="n"/>
     </row>
     <row r="458">
-      <c r="P458" s="6" t="n"/>
+      <c r="P458" s="5" t="n"/>
     </row>
     <row r="459">
-      <c r="P459" s="6" t="n"/>
+      <c r="P459" s="5" t="n"/>
     </row>
     <row r="460">
-      <c r="P460" s="6" t="n"/>
+      <c r="P460" s="5" t="n"/>
     </row>
     <row r="461">
-      <c r="P461" s="6" t="n"/>
+      <c r="P461" s="5" t="n"/>
     </row>
     <row r="462">
-      <c r="P462" s="6" t="n"/>
+      <c r="P462" s="5" t="n"/>
     </row>
     <row r="463">
-      <c r="P463" s="6" t="n"/>
+      <c r="P463" s="5" t="n"/>
     </row>
     <row r="464">
-      <c r="P464" s="6" t="n"/>
+      <c r="P464" s="5" t="n"/>
     </row>
     <row r="465">
-      <c r="P465" s="6" t="n"/>
+      <c r="P465" s="5" t="n"/>
     </row>
     <row r="466">
-      <c r="P466" s="6" t="n"/>
+      <c r="P466" s="5" t="n"/>
     </row>
     <row r="467">
-      <c r="P467" s="6" t="n"/>
+      <c r="P467" s="5" t="n"/>
     </row>
     <row r="468">
-      <c r="P468" s="6" t="n"/>
+      <c r="P468" s="5" t="n"/>
     </row>
     <row r="469">
-      <c r="P469" s="6" t="n"/>
+      <c r="P469" s="5" t="n"/>
     </row>
     <row r="470">
-      <c r="P470" s="6" t="n"/>
+      <c r="P470" s="5" t="n"/>
     </row>
     <row r="471">
-      <c r="P471" s="6" t="n"/>
+      <c r="P471" s="5" t="n"/>
     </row>
     <row r="472">
-      <c r="P472" s="6" t="n"/>
+      <c r="P472" s="5" t="n"/>
     </row>
     <row r="473">
-      <c r="P473" s="6" t="n"/>
+      <c r="P473" s="5" t="n"/>
     </row>
     <row r="474">
-      <c r="P474" s="6" t="n"/>
+      <c r="P474" s="5" t="n"/>
     </row>
     <row r="475">
-      <c r="P475" s="6" t="n"/>
+      <c r="P475" s="5" t="n"/>
     </row>
     <row r="476">
-      <c r="P476" s="6" t="n"/>
+      <c r="P476" s="5" t="n"/>
     </row>
     <row r="477">
-      <c r="P477" s="6" t="n"/>
+      <c r="P477" s="5" t="n"/>
     </row>
     <row r="478">
-      <c r="P478" s="6" t="n"/>
+      <c r="P478" s="5" t="n"/>
     </row>
     <row r="479">
-      <c r="P479" s="6" t="n"/>
+      <c r="P479" s="5" t="n"/>
     </row>
     <row r="480">
-      <c r="P480" s="6" t="n"/>
+      <c r="P480" s="5" t="n"/>
     </row>
     <row r="481">
-      <c r="P481" s="6" t="n"/>
+      <c r="P481" s="5" t="n"/>
     </row>
     <row r="482">
-      <c r="P482" s="6" t="n"/>
+      <c r="P482" s="5" t="n"/>
     </row>
     <row r="483">
-      <c r="P483" s="6" t="n"/>
+      <c r="P483" s="5" t="n"/>
     </row>
     <row r="484">
-      <c r="P484" s="6" t="n"/>
+      <c r="P484" s="5" t="n"/>
     </row>
     <row r="485">
-      <c r="P485" s="6" t="n"/>
+      <c r="P485" s="5" t="n"/>
     </row>
     <row r="486">
-      <c r="P486" s="6" t="n"/>
+      <c r="P486" s="5" t="n"/>
     </row>
     <row r="487">
-      <c r="P487" s="6" t="n"/>
+      <c r="P487" s="5" t="n"/>
     </row>
     <row r="488">
-      <c r="P488" s="6" t="n"/>
+      <c r="P488" s="5" t="n"/>
     </row>
     <row r="489">
-      <c r="P489" s="6" t="n"/>
+      <c r="P489" s="5" t="n"/>
     </row>
     <row r="490">
-      <c r="P490" s="6" t="n"/>
+      <c r="P490" s="5" t="n"/>
     </row>
     <row r="491">
-      <c r="P491" s="6" t="n"/>
+      <c r="P491" s="5" t="n"/>
     </row>
     <row r="492">
-      <c r="P492" s="6" t="n"/>
+      <c r="P492" s="5" t="n"/>
     </row>
     <row r="493">
-      <c r="P493" s="6" t="n"/>
+      <c r="P493" s="5" t="n"/>
     </row>
     <row r="494">
-      <c r="P494" s="6" t="n"/>
+      <c r="P494" s="5" t="n"/>
     </row>
     <row r="495">
-      <c r="P495" s="6" t="n"/>
+      <c r="P495" s="5" t="n"/>
     </row>
     <row r="496">
-      <c r="P496" s="6" t="n"/>
+      <c r="P496" s="5" t="n"/>
     </row>
     <row r="497">
-      <c r="P497" s="6" t="n"/>
+      <c r="P497" s="5" t="n"/>
     </row>
     <row r="498">
-      <c r="P498" s="6" t="n"/>
+      <c r="P498" s="5" t="n"/>
     </row>
     <row r="499">
-      <c r="P499" s="6" t="n"/>
+      <c r="P499" s="5" t="n"/>
     </row>
     <row r="500">
-      <c r="P500" s="6" t="n"/>
+      <c r="P500" s="5" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="O3:O500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not a recognised value" error="Use one of: available, notice_period, unavailable" type="list">
+    <dataValidation sqref="O2:O500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not a recognised value" error="Use one of: available, notice_period, unavailable" type="list">
       <formula1>"available,notice_period,unavailable"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q3:Q500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not a recognised value" error="Use one of: active, inactive, placed" type="list">
-      <formula1>"active,inactive,placed"</formula1>
+    <dataValidation sqref="Q2:Q500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not a recognised value" error="Use one of: active, inactive. Placed is set by the system when somebody is put on a contract." type="list">
+      <formula1>"active,inactive"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -2367,7 +2283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2377,527 +2293,544 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Candidate roster: what goes in each column</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Read this before filling anything in</t>
         </is>
       </c>
     </row>
     <row r="3" ht="118" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>If somebody already has a CV on the TiPP Focus template, upload the CV instead of typing them into this sheet. The system reads that template accurately and gets their full work history and education, which this sheet has no room for and which matters on a bid. Retyping a CV here produces a thinner record, not a faster one.
 This sheet earns its keep in two cases. People who have no CV yet, so there is nothing to upload. And the last five columns, which no CV carries: whether somebody is free, when they come free, whether they are still on the roster, which practice areas they sit in, and anything a resourcing conversation needs to know. Those can be filled in here for people whose CVs are already loaded, and left blank for everyone else.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Header colours on the Candidates tab</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>on the CV</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>only here</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Comes from</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>What it is</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Example</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="44" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+    <row r="7" ht="44" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>full_name</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>Required. The only column that cannot be blank. As it should read on a submitted CV.</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>Thandiwe Mokoena</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>Work or personal address.</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>t.mokoena@example.co.za</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>Any format.</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>082 555 0143</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>location</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>Where they are based.</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>Johannesburg</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>current_role</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>Their main role, spelled the way a tender would name it. This is the one that decides matching, so 'Business Analyst', never 'BA'.</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>ERP Consultant</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>additional_roles</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>Other roles they can be put forward for, separated by a pipe. Matching takes whichever scores best, so this genuinely widens what they can be bid on.</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>Business Analyst | Systems Analyst</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>years_experience</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>Whole years. Used against a seat's minimum.</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="44" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
+    <row r="14" ht="44" customHeight="1">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>designated_group</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t>Employment equity group, as it should read on a submitted CV. Matters on a BEE-scored bid.</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>African Female</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>qualifications</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>Degrees and diplomas, separated by a pipe.</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>BCom Information Systems | Matric</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="44" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
+    <row r="16" ht="44" customHeight="1">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>certifications</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>Certifications, separated by a pipe. Worth 20 of the 100 matching points.</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>Microsoft Certified: Dynamics 365 F&amp;O Apps Developer Associate</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>technical_skills</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>Tools, platforms and languages, separated by a pipe.</t>
         </is>
       </c>
-      <c r="D16" s="15" t="inlineStr">
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t>Microsoft Dynamics 365 | SQL | X++</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>skills</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <t>Professional and domain skills, separated by a pipe.</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>Business Process Analysis | UAT</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>sectors</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>Sectors they have worked in, separated by a pipe.</t>
         </is>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>Public Sector | Finance</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>languages</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C20" s="15" t="inlineStr">
         <is>
           <t>Separated by a pipe.</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>English | Setswana</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="44" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
+    <row r="21" ht="44" customHeight="1">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>availability</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B21" s="18" t="inlineStr">
         <is>
           <t>Only here</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C21" s="15" t="inlineStr">
         <is>
           <t>One of: available, notice_period, unavailable. Pick from the dropdown. Blank is read as available.</t>
         </is>
       </c>
-      <c r="D20" s="15" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>available</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>available_from</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>Only here</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C22" s="15" t="inlineStr">
         <is>
           <t>The date they next come free, if they are committed now. Leave blank if free today. Year, then month, then day.</t>
         </is>
       </c>
-      <c r="D21" s="15" t="inlineStr">
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>2027-03-01</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B23" s="18" t="inlineStr">
         <is>
           <t>Only here</t>
         </is>
       </c>
-      <c r="C22" s="14" t="inlineStr">
-        <is>
-          <t>One of: active, inactive, placed. Blank is read as active. Inactive takes somebody out of matching without deleting them.</t>
-        </is>
-      </c>
-      <c r="D22" s="15" t="inlineStr">
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>One of: active or inactive. Blank is read as active. Inactive takes somebody out of matching without deleting them. Placed is not typed here: the system sets it when somebody is actually put on a contract.</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>resource_categories</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B24" s="18" t="inlineStr">
         <is>
           <t>Only here</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>Practice areas, separated by a pipe. Used for the bench view and reporting. One of: ERP, Enterprise Architecture (EA), Software Development, Data &amp; BI, Cloud &amp; DevOps, Cybersecurity, Project &amp; Programme Management, Business Analysis, Finance &amp; Accounting, Construction &amp; Engineering.</t>
         </is>
       </c>
-      <c r="D23" s="15" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>ERP | Business Analysis</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="12" t="inlineStr">
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B25" s="18" t="inlineStr">
         <is>
           <t>Only here</t>
         </is>
       </c>
-      <c r="C24" s="14" t="inlineStr">
+      <c r="C25" s="15" t="inlineStr">
         <is>
           <t>Anything a resourcing conversation needs. Free text.</t>
         </is>
       </c>
-      <c r="D24" s="15" t="inlineStr">
+      <c r="D25" s="16" t="inlineStr">
         <is>
           <t>Strong on D365 Finance. Prefers Gauteng-based work.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>Three things that cause trouble</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="68" customHeight="1">
-      <c r="A27" s="18" t="inlineStr">
+    <row r="28" ht="68" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>Role names decide everything</t>
         </is>
       </c>
-      <c r="C27" s="10" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>current_role is compared against the role on a tender seat. It scores full marks for an exact match and nothing at all for a spelling the system does not know, and role is 35 of the 100 matching points. Somebody entered as 'Snr BA' will never come up as a strong match for a Business Analyst seat, and nothing on screen will explain why. Write the role out.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="68" customHeight="1">
-      <c r="A28" s="18" t="inlineStr">
+    <row r="29" ht="68" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>Dates must read 2027-03-01</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>Year, then month, then day. Only available_from is a date, and only for people who are committed right now.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="68" customHeight="1">
-      <c r="A29" s="18" t="inlineStr">
+    <row r="30" ht="68" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>Use a pipe between list items</t>
         </is>
       </c>
-      <c r="C29" s="10" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>Every list column separates with a pipe, not a comma, so a qualification like 'BCom Information Systems, Cum Laude' stays as one thing.</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>When it is filled in: save as CSV (File, Save As, CSV UTF-8) and send that. Nothing is written to the system until the file has been read back to you first.</t>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>When it is filled in: save as CSV (File, Save As, CSV UTF-8) and send that. It is read with  npx tsx scripts/import-candidates.ts &lt;file.csv&gt;  which prints back exactly what it would do and writes nothing. Only a second run with --apply writes. For anybody who already has a CV on file, it fills in a blank column and never overwrites what the CV said, and the report names every column it left alone.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A27:D27"/>
     <mergeCell ref="C29:D29"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C30:D30"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
